--- a/wwwroot/ExcelLoading/Loadding.xlsx
+++ b/wwwroot/ExcelLoading/Loadding.xlsx
@@ -43,25 +43,31 @@
     <x:t>UOM</x:t>
   </x:si>
   <x:si>
-    <x:t>F011001601.230324MP3BMP3A.C.0</x:t>
+    <x:t>290324MP3A</x:t>
   </x:si>
   <x:si>
     <x:t>TVO1</x:t>
   </x:si>
   <x:si>
-    <x:t>C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TVO Dehulled soymeal (TH) Bulk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1300 BAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23/03/2024</x:t>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TVO Dehulled soymeal (TH) 70 Kg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70 BAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29/03/2024</x:t>
   </x:si>
   <x:si>
     <x:t>BAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70 BOX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOX</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -412,7 +418,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I2"/>
+  <x:dimension ref="A1:I3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -449,7 +455,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>10</x:v>
@@ -471,6 +477,35 @@
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
+      <x:c r="A3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
